--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5E4D13-2BDA-4FA1-9AE8-37F3F9714FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9E1A92-C93F-4110-A942-C90B0B09021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3012" yWindow="1116" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2784" yWindow="1296" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>float[]</t>
   </si>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>2DObject/Zobie</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -197,7 +209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -229,12 +241,6 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -325,7 +331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -350,12 +356,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -835,7 +840,9 @@
       <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:19" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="12" t="s">
@@ -859,13 +866,15 @@
       <c r="G3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="15" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -889,13 +898,15 @@
       <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="J4" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -928,11 +939,13 @@
       <c r="G5" s="6">
         <v>0</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -965,9 +978,11 @@
       <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -1000,9 +1015,11 @@
       <c r="G7" s="7">
         <v>0</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -1035,9 +1052,11 @@
       <c r="G8" s="7">
         <v>0</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -1070,9 +1089,11 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1105,9 +1126,11 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -1119,6 +1142,8 @@
       <c r="S10" s="5"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" customHeight="1">
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9E1A92-C93F-4110-A942-C90B0B09021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DADD73-468E-4135-864D-14BCD16054B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2784" yWindow="1296" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2976" yWindow="3012" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DADD73-468E-4135-864D-14BCD16054B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588DA876-112A-472A-BE27-6BC25EEBE91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2976" yWindow="3012" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="1716" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>float[]</t>
   </si>
@@ -165,10 +165,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -202,6 +198,25 @@
   </si>
   <si>
     <t>Special</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Zobie_Beast</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Zobie_Barmour</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Zobie_Mimic</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Zobie_Thromer</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Zobie_auger</t>
+  </si>
+  <si>
+    <t>float[]</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -829,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>6</v>
@@ -867,13 +882,13 @@
         <v>38</v>
       </c>
       <c r="H3" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="15" t="s">
-        <v>42</v>
-      </c>
       <c r="J3" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1">
@@ -899,13 +914,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -940,11 +955,11 @@
         <v>0</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5" s="16"/>
       <c r="J5" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -978,10 +993,12 @@
       <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="16"/>
+      <c r="H6" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="I6" s="16"/>
       <c r="J6" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -1015,10 +1032,12 @@
       <c r="G7" s="7">
         <v>0</v>
       </c>
-      <c r="H7" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -1052,10 +1071,12 @@
       <c r="G8" s="7">
         <v>0</v>
       </c>
-      <c r="H8" s="16"/>
+      <c r="H8" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -1089,10 +1110,12 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -1126,10 +1149,12 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="16"/>
+      <c r="H10" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
